--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260923.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.98%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.84%</t>
         </is>
       </c>
     </row>
@@ -660,73 +660,73 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>6,331,000</t>
+          <t>51,253,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>22,333,000</t>
+          <t>6,331,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.02%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>51,253,000</t>
+          <t>22,838,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>37,372,000</t>
+          <t>38,129,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -777,22 +777,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,299,222,641</t>
+          <t>27,928,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -814,29 +814,29 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>27,284,000</t>
+          <t>3,949,286,494</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.54%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.53%</t>
         </is>
       </c>
     </row>
@@ -875,78 +875,78 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>36,182,000</t>
+          <t>36,729,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>33,103,000</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>33,103,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.43%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>2,939,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -990,95 +990,95 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>23,080,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,322,000</t>
+          <t>23,080,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>2,322,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,939,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -1100,156 +1100,156 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,893,000</t>
+          <t>4,409,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>4,409,000</t>
+          <t>4,784,400</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>9,893,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,578,000</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>健鼎科技</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>4,784,400</t>
+          <t>5,434,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>健鼎科技</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>5,434,000</t>
+          <t>15,578,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯華電子</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>17,775,000</t>
+          <t>2,846,951,204</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>聯華電子</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,837,381,204</t>
+          <t>17,775,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,39 +1283,39 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,795,000</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.66%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>6,795,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>10,015,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1364,68 +1364,68 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>10,015,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>6,478,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,901,000</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,22 +1437,22 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>3,901,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1496,51 +1496,51 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>23,694,000</t>
+          <t>15,340,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>15,340,000</t>
+          <t>23,694,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1628,24 +1628,24 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>18,948,000</t>
+          <t>54,146,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,61 +1657,61 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>54,146,000</t>
+          <t>18,948,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>20,037,000</t>
+          <t>17,681,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>17,681,000</t>
+          <t>20,037,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
